--- a/data/trans_orig/P36BPD13_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD13_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si consumen preferentemente carne de pollo, pavo o conejo en vez de ternera, cerdo, hamburguesas o salchichas en 2023</t>
+          <t>Población según si consumen preferentemente carne de pollo, pavo o conejo en vez de ternera, cerdo, hamburguesas o salchichas en 2023 (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>561183</t>
+          <t>560328</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>593540</t>
+          <t>592050</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>609329</t>
+          <t>608522</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>632298</t>
+          <t>631677</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1179096</t>
+          <t>1178387</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1218569</t>
+          <t>1218542</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39258</t>
+          <t>40748</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>71615</t>
+          <t>72470</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38072</t>
+          <t>38693</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61041</t>
+          <t>61848</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>84600</t>
+          <t>84627</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>124073</t>
+          <t>124782</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1025407</t>
+          <t>1025045</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1125171</t>
+          <t>1125848</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>840233</t>
+          <t>841533</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>873793</t>
+          <t>873504</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1884586</t>
+          <t>1882270</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1997758</t>
+          <t>1994763</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,18%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>63027</t>
+          <t>62350</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>162791</t>
+          <t>163153</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>78688</t>
+          <t>78977</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>112248</t>
+          <t>110948</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>142921</t>
+          <t>145916</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>256093</t>
+          <t>258409</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>481026</t>
+          <t>479615</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>534693</t>
+          <t>536416</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>761911</t>
+          <t>762467</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>862455</t>
+          <t>873141</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1255705</t>
+          <t>1254752</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1427284</t>
+          <t>1422775</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,45%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>165128</t>
+          <t>163405</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>218795</t>
+          <t>220206</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>64598</t>
+          <t>53912</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165142</t>
+          <t>164586</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>199590</t>
+          <t>204099</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>371169</t>
+          <t>372122</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,87%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>756257</t>
+          <t>752944</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>803942</t>
+          <t>802346</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>926691</t>
+          <t>923638</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>979284</t>
+          <t>975436</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1691733</t>
+          <t>1693595</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1761856</t>
+          <t>1763950</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>88,0%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>115097</t>
+          <t>116693</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>162782</t>
+          <t>166095</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>106202</t>
+          <t>110050</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>158795</t>
+          <t>161848</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>242669</t>
+          <t>240575</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>312792</t>
+          <t>310930</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,51%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2875657</t>
+          <t>2868463</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3044662</t>
+          <t>3037284</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3189337</t>
+          <t>3188872</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3307672</t>
+          <t>3303712</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6087588</t>
+          <t>6088937</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6310817</t>
+          <t>6286971</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>88,86%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>395194</t>
+          <t>402572</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>564199</t>
+          <t>571393</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>327718</t>
+          <t>331678</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>446053</t>
+          <t>446518</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>764429</t>
+          <t>788275</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>987658</t>
+          <t>986309</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,94%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD13_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD13_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>579029</t>
+          <t>629152</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>560328</t>
+          <t>609950</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>592050</t>
+          <t>643058</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>621396</t>
+          <t>674188</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>608522</t>
+          <t>659400</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>631677</t>
+          <t>684769</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1200426</t>
+          <t>1303341</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1178387</t>
+          <t>1279612</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1218542</t>
+          <t>1322603</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,44%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>53769</t>
+          <t>58718</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40748</t>
+          <t>44812</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>72470</t>
+          <t>77920</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>48974</t>
+          <t>53428</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38693</t>
+          <t>42847</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61848</t>
+          <t>68216</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>102743</t>
+          <t>112146</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>84627</t>
+          <t>92884</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>124782</t>
+          <t>135875</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,6%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>632798</t>
+          <t>687870</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>632798</t>
+          <t>687870</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>632798</t>
+          <t>687870</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>670370</t>
+          <t>727616</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>670370</t>
+          <t>727616</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>670370</t>
+          <t>727616</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1303169</t>
+          <t>1415487</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1303169</t>
+          <t>1415487</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1303169</t>
+          <t>1415487</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1067809</t>
+          <t>914199</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1025045</t>
+          <t>889390</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1125848</t>
+          <t>939480</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>858498</t>
+          <t>959056</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>841533</t>
+          <t>940819</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>873504</t>
+          <t>975384</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1926307</t>
+          <t>1873255</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1882270</t>
+          <t>1841651</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1994763</t>
+          <t>1901444</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>90,19%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>120389</t>
+          <t>129682</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>62350</t>
+          <t>104401</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>163153</t>
+          <t>154491</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>93983</t>
+          <t>105246</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>78977</t>
+          <t>88918</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>110948</t>
+          <t>123483</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>214372</t>
+          <t>234928</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>145916</t>
+          <t>206739</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>258409</t>
+          <t>266532</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,64%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1188198</t>
+          <t>1043881</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1188198</t>
+          <t>1043881</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1188198</t>
+          <t>1043881</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>952481</t>
+          <t>1064302</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>952481</t>
+          <t>1064302</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>952481</t>
+          <t>1064302</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2140679</t>
+          <t>2108183</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2140679</t>
+          <t>2108183</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2140679</t>
+          <t>2108183</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>509461</t>
+          <t>590782</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>479615</t>
+          <t>562533</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>536416</t>
+          <t>617240</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>70,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>805567</t>
+          <t>663103</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>762467</t>
+          <t>644388</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>873141</t>
+          <t>683595</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1315028</t>
+          <t>1253886</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1254752</t>
+          <t>1218291</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1422775</t>
+          <t>1289433</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>80,52%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>190360</t>
+          <t>206188</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>163405</t>
+          <t>179730</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>220206</t>
+          <t>234437</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>121486</t>
+          <t>141341</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>53912</t>
+          <t>120849</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>164586</t>
+          <t>160056</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>311846</t>
+          <t>347529</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>204099</t>
+          <t>311982</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>372122</t>
+          <t>383124</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>23,92%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>699821</t>
+          <t>796970</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>699821</t>
+          <t>796970</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>699821</t>
+          <t>796970</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>927053</t>
+          <t>804444</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>927053</t>
+          <t>804444</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>927053</t>
+          <t>804444</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1626874</t>
+          <t>1601415</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1626874</t>
+          <t>1601415</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1626874</t>
+          <t>1601415</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>780306</t>
+          <t>834243</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>752944</t>
+          <t>807279</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>802346</t>
+          <t>857191</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>948196</t>
+          <t>955352</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>923638</t>
+          <t>933552</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>975436</t>
+          <t>975711</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1728503</t>
+          <t>1789594</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1693595</t>
+          <t>1755342</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1763950</t>
+          <t>1820240</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>87,03%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>138733</t>
+          <t>148550</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>116693</t>
+          <t>125602</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>166095</t>
+          <t>175514</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>137290</t>
+          <t>153403</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>110050</t>
+          <t>133044</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>161848</t>
+          <t>175203</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>276022</t>
+          <t>301953</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>240575</t>
+          <t>271307</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>310930</t>
+          <t>336205</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>16,07%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>919039</t>
+          <t>982793</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>919039</t>
+          <t>982793</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>919039</t>
+          <t>982793</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1085486</t>
+          <t>1108755</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1085486</t>
+          <t>1108755</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1085486</t>
+          <t>1108755</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2004525</t>
+          <t>2091547</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2004525</t>
+          <t>2091547</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2004525</t>
+          <t>2091547</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2936605</t>
+          <t>2968376</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2868463</t>
+          <t>2919385</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3037284</t>
+          <t>3018999</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3233657</t>
+          <t>3251699</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3188872</t>
+          <t>3216731</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3303712</t>
+          <t>3288283</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>6170262</t>
+          <t>6220076</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6088937</t>
+          <t>6159518</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6286971</t>
+          <t>6280462</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>87,03%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>503251</t>
+          <t>543139</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>402572</t>
+          <t>492516</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>571393</t>
+          <t>592130</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>401733</t>
+          <t>453418</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>331678</t>
+          <t>416834</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>446518</t>
+          <t>488386</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>904984</t>
+          <t>996556</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>788275</t>
+          <t>936170</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>986309</t>
+          <t>1057114</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,65%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3439856</t>
+          <t>3511515</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3439856</t>
+          <t>3511515</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3439856</t>
+          <t>3511515</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3635390</t>
+          <t>3705117</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3635390</t>
+          <t>3705117</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3635390</t>
+          <t>3705117</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7075246</t>
+          <t>7216632</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7075246</t>
+          <t>7216632</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7075246</t>
+          <t>7216632</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
